--- a/data/trans_orig/Q23_tabaco_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38592</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59605</t>
+          <t>59863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>28238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53690</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82762</t>
+          <t>80546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73044</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94057</t>
+          <t>95289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>48786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64861</t>
+          <t>64790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126911</t>
+          <t>129127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155983</t>
+          <t>156737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93445</t>
+          <t>93861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129514</t>
+          <t>125965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48020</t>
+          <t>48862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127572</t>
+          <t>127943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166383</t>
+          <t>168473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>139206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171726</t>
+          <t>171310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85646</t>
+          <t>84804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105668</t>
+          <t>105400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232454</t>
+          <t>230364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>271265</t>
+          <t>270894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55675</t>
+          <t>56221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81395</t>
+          <t>80760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78877</t>
+          <t>78217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109288</t>
+          <t>109965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89190</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114910</t>
+          <t>114364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81162</t>
+          <t>81271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160750</t>
+          <t>160073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191161</t>
+          <t>191821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76429</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36306</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73651</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105402</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127504</t>
+          <t>126941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154212</t>
+          <t>153658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93844</t>
+          <t>94069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111559</t>
+          <t>111328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228906</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>260657</t>
+          <t>261092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>56974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>71232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88367</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44389</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60682</t>
+          <t>59974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120359</t>
+          <t>121240</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>144366</t>
+          <t>144332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>50351</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75487</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72383</t>
+          <t>69777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102859</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80734</t>
+          <t>80652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104729</t>
+          <t>105788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>45841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>61270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130158</t>
+          <t>132340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160634</t>
+          <t>163240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89819</t>
+          <t>88862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122573</t>
+          <t>124712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>40955</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64230</t>
+          <t>64480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139799</t>
+          <t>135588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178379</t>
+          <t>178608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>176436</t>
+          <t>174297</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209190</t>
+          <t>210147</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122151</t>
+          <t>121901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147139</t>
+          <t>145426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307011</t>
+          <t>306782</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>345591</t>
+          <t>349802</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108624</t>
+          <t>110816</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145679</t>
+          <t>146304</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43494</t>
+          <t>44198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70076</t>
+          <t>68954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159898</t>
+          <t>160066</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206758</t>
+          <t>206850</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244221</t>
+          <t>243596</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281276</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149973</t>
+          <t>151095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176555</t>
+          <t>175851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>403191</t>
+          <t>403099</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>450051</t>
+          <t>449883</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>568525</t>
+          <t>572225</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>650850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292311</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>816937</t>
+          <t>820550</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919160</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1073197</t>
+          <t>1070214</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1152539</t>
+          <t>1148839</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>706059</t>
+          <t>706053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>761677</t>
+          <t>763423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1802443</t>
+          <t>1800267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1902490</t>
+          <t>1898877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58930</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86974</t>
+          <t>86133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31164</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>54377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>96910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>131724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95098</t>
+          <t>95939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123142</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71728</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95613</t>
+          <t>97105</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175653</t>
+          <t>177124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212147</t>
+          <t>211938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119485</t>
+          <t>120846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156948</t>
+          <t>159226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>50712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>78017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179027</t>
+          <t>179235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226408</t>
+          <t>226377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165522</t>
+          <t>163244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202985</t>
+          <t>201624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126770</t>
+          <t>126879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155290</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>300990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348340</t>
+          <t>348132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59124</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87624</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41053</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86458</t>
+          <t>85798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>121759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121344</t>
+          <t>121183</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149844</t>
+          <t>149460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78667</t>
+          <t>77223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>99086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207552</t>
+          <t>206928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242229</t>
+          <t>242889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57436</t>
+          <t>57684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87345</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36934</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79670</t>
+          <t>79783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116483</t>
+          <t>116713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123101</t>
+          <t>123560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153010</t>
+          <t>152762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109700</t>
+          <t>109841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129419</t>
+          <t>129390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240597</t>
+          <t>240367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277410</t>
+          <t>277297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44863</t>
+          <t>43873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69397</t>
+          <t>68274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>40254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72225</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104488</t>
+          <t>103022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>70637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>95038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52422</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70345</t>
+          <t>70861</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126715</t>
+          <t>128181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158978</t>
+          <t>158847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73451</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>72654</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102856</t>
+          <t>103831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91511</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116615</t>
+          <t>116055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>68208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148209</t>
+          <t>147234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179529</t>
+          <t>178411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127527</t>
+          <t>129308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169690</t>
+          <t>169785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62108</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>93216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202391</t>
+          <t>200437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251905</t>
+          <t>251746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246831</t>
+          <t>246736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288994</t>
+          <t>287213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>179038</t>
+          <t>179165</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>210273</t>
+          <t>210226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>436998</t>
+          <t>437157</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>486512</t>
+          <t>488466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131555</t>
+          <t>131113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>55360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86144</t>
+          <t>86685</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157830</t>
+          <t>157793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206773</t>
+          <t>206034</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268437</t>
+          <t>268879</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>303230</t>
+          <t>306103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>182484</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>212777</t>
+          <t>213268</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>461847</t>
+          <t>462586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>510790</t>
+          <t>510827</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>687193</t>
+          <t>689918</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>775790</t>
+          <t>780342</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>402629</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1036339</t>
+          <t>1041138</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1150041</t>
+          <t>1156243</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1268552</t>
+          <t>1264000</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1357149</t>
+          <t>1354424</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>916041</t>
+          <t>914802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>986340</t>
+          <t>986094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2211732</t>
+          <t>2205530</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2325434</t>
+          <t>2320635</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76804</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104569</t>
+          <t>104249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55650</t>
+          <t>55598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>116170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153160</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71360</t>
+          <t>71680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99125</t>
+          <t>98141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>70894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92900</t>
+          <t>93931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149261</t>
+          <t>149680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185439</t>
+          <t>186251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75782</t>
+          <t>74084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107783</t>
+          <t>106311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35668</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60435</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118707</t>
+          <t>117351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157540</t>
+          <t>158554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173668</t>
+          <t>175140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205669</t>
+          <t>207367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114232</t>
+          <t>115041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138999</t>
+          <t>138919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>298578</t>
+          <t>297564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337411</t>
+          <t>338767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37753</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61160</t>
+          <t>61650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>64138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92910</t>
+          <t>92539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94608</t>
+          <t>94118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118015</t>
+          <t>117248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66293</t>
+          <t>65852</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84237</t>
+          <t>84102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>168571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195890</t>
+          <t>196972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79715</t>
+          <t>79199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110450</t>
+          <t>109806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54624</t>
+          <t>54799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117109</t>
+          <t>117918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156120</t>
+          <t>156615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122235</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152970</t>
+          <t>153486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101859</t>
+          <t>101684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124806</t>
+          <t>124696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233048</t>
+          <t>232553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272059</t>
+          <t>271250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27632</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47313</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27794</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70678</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68441</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88122</t>
+          <t>87419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>58553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117089</t>
+          <t>117052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143118</t>
+          <t>141979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37968</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62806</t>
+          <t>63784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84301</t>
+          <t>84945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105467</t>
+          <t>105928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67823</t>
+          <t>68527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>81229</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159074</t>
+          <t>158096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>183912</t>
+          <t>183673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86810</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122447</t>
+          <t>120971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45304</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72713</t>
+          <t>72751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139435</t>
+          <t>139598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184178</t>
+          <t>182699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190597</t>
+          <t>192073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226234</t>
+          <t>227508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>176375</t>
+          <t>176337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203784</t>
+          <t>203286</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>377954</t>
+          <t>379433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>422697</t>
+          <t>422534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116217</t>
+          <t>117711</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>157424</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57822</t>
+          <t>56847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87447</t>
+          <t>87513</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184368</t>
+          <t>182814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231315</t>
+          <t>230841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205255</t>
+          <t>202950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>244157</t>
+          <t>242663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184921</t>
+          <t>184855</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214546</t>
+          <t>215521</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>401427</t>
+          <t>401901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>448374</t>
+          <t>449928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>598752</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>679504</t>
+          <t>681670</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>292931</t>
+          <t>291263</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>355893</t>
+          <t>356031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>903152</t>
+          <t>904954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1014274</t>
+          <t>1013420</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1089335</t>
+          <t>1087169</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1170087</t>
+          <t>1170492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>888607</t>
+          <t>888469</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>951569</t>
+          <t>953237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1999065</t>
+          <t>1999919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2110187</t>
+          <t>2108385</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46347</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72532</t>
+          <t>75543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60846</t>
+          <t>61287</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89826</t>
+          <t>93119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59362</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85547</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54473</t>
+          <t>54745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65649</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119186</t>
+          <t>115893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148166</t>
+          <t>147725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>62499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102828</t>
+          <t>99601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33591</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55240</t>
+          <t>54296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>104635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147490</t>
+          <t>146072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142173</t>
+          <t>145400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180858</t>
+          <t>182502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108956</t>
+          <t>109900</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130605</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>261707</t>
+          <t>263125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>302815</t>
+          <t>304562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58713</t>
+          <t>58454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80705</t>
+          <t>79500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34560</t>
+          <t>34692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81957</t>
+          <t>82320</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109320</t>
+          <t>108846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58509</t>
+          <t>59714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80501</t>
+          <t>80760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>75399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90963</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139985</t>
+          <t>140459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167348</t>
+          <t>166985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54516</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84051</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116935</t>
+          <t>116342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139414</t>
+          <t>138531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88102</t>
+          <t>88588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107126</t>
+          <t>107374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212267</t>
+          <t>212439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241802</t>
+          <t>242097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>31415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31541</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70411</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42089</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>59651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24460</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57224</t>
+          <t>58483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79825</t>
+          <t>80155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59394</t>
+          <t>60787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78349</t>
+          <t>78995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99715</t>
+          <t>99385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122316</t>
+          <t>121057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>91288</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127971</t>
+          <t>128999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56268</t>
+          <t>56839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84138</t>
+          <t>84453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>154638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203460</t>
+          <t>204642</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163709</t>
+          <t>162681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201851</t>
+          <t>200392</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>160859</t>
+          <t>160544</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188729</t>
+          <t>188158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>333217</t>
+          <t>332035</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>379650</t>
+          <t>382039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136286</t>
+          <t>135273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31617</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149666</t>
+          <t>148285</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>388593</t>
+          <t>389606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>506097</t>
+          <t>504998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120700</t>
+          <t>120267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136246</t>
+          <t>136150</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>526856</t>
+          <t>528237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>644905</t>
+          <t>643627</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>298145</t>
+          <t>296898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>583493</t>
+          <t>587979</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>212404</t>
+          <t>210736</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>259085</t>
+          <t>259962</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>523840</t>
+          <t>509845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>815602</t>
+          <t>811062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1086127</t>
+          <t>1081641</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1371475</t>
+          <t>1372722</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>714626</t>
+          <t>713749</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>761307</t>
+          <t>762975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1827729</t>
+          <t>1832269</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2119491</t>
+          <t>2133486</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>37513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59863</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28238</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52936</t>
+          <t>55301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80546</t>
+          <t>83402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95289</t>
+          <t>95136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48786</t>
+          <t>48536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64790</t>
+          <t>64670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129127</t>
+          <t>126271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156737</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93861</t>
+          <t>93983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125965</t>
+          <t>128079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48862</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127943</t>
+          <t>126852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168473</t>
+          <t>166356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139206</t>
+          <t>137092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171310</t>
+          <t>171188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84804</t>
+          <t>85571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105400</t>
+          <t>106250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230364</t>
+          <t>232481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270894</t>
+          <t>271985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>55603</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80760</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>34655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78217</t>
+          <t>78502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109965</t>
+          <t>108893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89825</t>
+          <t>89404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114364</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64220</t>
+          <t>64798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>81969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160073</t>
+          <t>161145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191821</t>
+          <t>191536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50275</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>76270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36306</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>73521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105375</t>
+          <t>104625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126941</t>
+          <t>127663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153658</t>
+          <t>154065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94069</t>
+          <t>94806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111328</t>
+          <t>113018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228933</t>
+          <t>229683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261092</t>
+          <t>260787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>32103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30159</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>71575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88314</t>
+          <t>87763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44378</t>
+          <t>44375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59974</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121240</t>
+          <t>120810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>144076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50351</t>
+          <t>51522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75487</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69777</t>
+          <t>71887</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>100782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>80952</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>44884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61270</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132340</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163240</t>
+          <t>161130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88862</t>
+          <t>91578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124712</t>
+          <t>125246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40955</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64480</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135588</t>
+          <t>136153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178608</t>
+          <t>179368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174297</t>
+          <t>173763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210147</t>
+          <t>207431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121901</t>
+          <t>121289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145426</t>
+          <t>145675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>306782</t>
+          <t>306022</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>349802</t>
+          <t>349237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110816</t>
+          <t>108643</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146304</t>
+          <t>145739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44198</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68954</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160066</t>
+          <t>161554</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206850</t>
+          <t>206707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>243596</t>
+          <t>244161</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>279084</t>
+          <t>281257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151095</t>
+          <t>149530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>175851</t>
+          <t>176589</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>403099</t>
+          <t>403242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>449883</t>
+          <t>448395</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>572225</t>
+          <t>567441</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>650850</t>
+          <t>653171</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>292311</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>820550</t>
+          <t>821881</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>919160</t>
+          <t>921289</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1070214</t>
+          <t>1067893</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1148839</t>
+          <t>1153623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>706053</t>
+          <t>708290</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>763423</t>
+          <t>763517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1800267</t>
+          <t>1798138</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1898877</t>
+          <t>1897546</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58966</t>
+          <t>58468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86133</t>
+          <t>86771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>55586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96910</t>
+          <t>96289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131724</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>95301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123106</t>
+          <t>123604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72400</t>
+          <t>71191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97105</t>
+          <t>95198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177124</t>
+          <t>176764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211938</t>
+          <t>212559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120846</t>
+          <t>119934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159226</t>
+          <t>157154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50712</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78017</t>
+          <t>78519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179235</t>
+          <t>180659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226377</t>
+          <t>227820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163244</t>
+          <t>165316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201624</t>
+          <t>202536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126879</t>
+          <t>126377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154184</t>
+          <t>154012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300990</t>
+          <t>299547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348132</t>
+          <t>346708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>59048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87785</t>
+          <t>88086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42497</t>
+          <t>41666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85798</t>
+          <t>88398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121759</t>
+          <t>123223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>120882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149460</t>
+          <t>149920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77223</t>
+          <t>78054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99086</t>
+          <t>98385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>206928</t>
+          <t>205464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242889</t>
+          <t>240289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,11%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57684</t>
+          <t>57929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86886</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36793</t>
+          <t>37394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79783</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116713</t>
+          <t>117453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123560</t>
+          <t>123046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152762</t>
+          <t>152517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109841</t>
+          <t>109240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129390</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240367</t>
+          <t>239627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277297</t>
+          <t>275096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43873</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68274</t>
+          <t>68902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72356</t>
+          <t>71231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103022</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70637</t>
+          <t>70009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95038</t>
+          <t>94053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>52529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70861</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128181</t>
+          <t>130198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158847</t>
+          <t>159972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48907</t>
+          <t>49005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73591</t>
+          <t>73408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34885</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72654</t>
+          <t>71189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103831</t>
+          <t>100763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>91554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116055</t>
+          <t>115957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51218</t>
+          <t>51055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68208</t>
+          <t>68585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147234</t>
+          <t>150302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178411</t>
+          <t>179876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129308</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169785</t>
+          <t>169963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93216</t>
+          <t>94587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>200437</t>
+          <t>199718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251746</t>
+          <t>249739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246736</t>
+          <t>246558</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287213</t>
+          <t>286731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>179165</t>
+          <t>177794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>210226</t>
+          <t>209051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437157</t>
+          <t>439164</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>488466</t>
+          <t>489185</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93889</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131113</t>
+          <t>132423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55360</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86685</t>
+          <t>84362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>160315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206034</t>
+          <t>205808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268879</t>
+          <t>267569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>306103</t>
+          <t>303771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>181943</t>
+          <t>184266</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>213268</t>
+          <t>212567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>462586</t>
+          <t>462812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>510827</t>
+          <t>508305</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>689918</t>
+          <t>691164</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>780342</t>
+          <t>779873</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331478</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>402629</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1041138</t>
+          <t>1045128</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1156243</t>
+          <t>1159739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1264000</t>
+          <t>1264469</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1354424</t>
+          <t>1353178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>914802</t>
+          <t>917384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>986094</t>
+          <t>985953</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2205530</t>
+          <t>2202034</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2320635</t>
+          <t>2316645</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77788</t>
+          <t>77748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104249</t>
+          <t>103976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116170</t>
+          <t>116778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>152350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71680</t>
+          <t>71953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98141</t>
+          <t>98181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>71756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>93465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149680</t>
+          <t>150071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186251</t>
+          <t>185643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74084</t>
+          <t>75991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106311</t>
+          <t>108825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,82 +7737,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>47464</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36172</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>60107</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>20,71%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>138194</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>120040</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>161079</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>30,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>26,32%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47464</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>35748</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>59626</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>20,47%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>34,14%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>138194</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>117351</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>158554</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>30,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175140</t>
+          <t>172626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207367</t>
+          <t>205460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,82 +7850,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>73,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>127203</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>114560</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>138495</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>72,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>79,29%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>317924</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>295039</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>336078</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>69,7%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>73,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>127203</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>115041</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>138919</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>65,86%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>317924</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>297564</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>338767</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>69,7%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38520</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61650</t>
+          <t>59748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64138</t>
+          <t>66057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92539</t>
+          <t>94170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94118</t>
+          <t>96020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117248</t>
+          <t>117870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65852</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84102</t>
+          <t>84753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>166940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196972</t>
+          <t>195053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79199</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109806</t>
+          <t>110619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>54403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,47 +8458,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>136303</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>117641</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>155306</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>35,02%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>136303</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>117918</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>156615</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>35,02%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122879</t>
+          <t>122066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153486</t>
+          <t>153981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101684</t>
+          <t>102080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124696</t>
+          <t>125893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,47 +8571,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>65,23%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>252865</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>233862</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>271527</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>64,98%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>79,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>252865</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>232553</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>271250</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>64,98%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>47229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45788</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70715</t>
+          <t>69794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67591</t>
+          <t>68525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87419</t>
+          <t>87737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44245</t>
+          <t>44120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58553</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117052</t>
+          <t>117973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141979</t>
+          <t>142568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48889</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>37924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63784</t>
+          <t>62251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84945</t>
+          <t>84412</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105928</t>
+          <t>105667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68527</t>
+          <t>68179</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81229</t>
+          <t>81444</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>159629</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>183673</t>
+          <t>183956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>86119</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120971</t>
+          <t>122784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45802</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72751</t>
+          <t>72966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139598</t>
+          <t>139444</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182699</t>
+          <t>184726</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192073</t>
+          <t>190260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227508</t>
+          <t>226925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>176337</t>
+          <t>176122</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203286</t>
+          <t>203367</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>379433</t>
+          <t>377406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>422534</t>
+          <t>422688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117711</t>
+          <t>117571</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157424</t>
+          <t>154971</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56847</t>
+          <t>57387</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87513</t>
+          <t>85440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182814</t>
+          <t>183073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>230841</t>
+          <t>233015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>202950</t>
+          <t>205403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>242663</t>
+          <t>242803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184855</t>
+          <t>186928</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>215521</t>
+          <t>214981</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>401901</t>
+          <t>399727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>449928</t>
+          <t>449669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>598347</t>
+          <t>596422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>681670</t>
+          <t>678993</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>291263</t>
+          <t>295955</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>356031</t>
+          <t>357459</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>904954</t>
+          <t>908851</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1013420</t>
+          <t>1015207</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1087169</t>
+          <t>1089846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1170492</t>
+          <t>1172417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>888469</t>
+          <t>887041</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>953237</t>
+          <t>948545</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1999919</t>
+          <t>1998132</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2108385</t>
+          <t>2104488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47152</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>62201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22373</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>68124</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61287</t>
+          <t>56164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93119</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73362</t>
+          <t>74958</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>64111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84742</t>
+          <t>86626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60758</t>
+          <t>61999</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54745</t>
+          <t>55839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>134120</t>
+          <t>136957</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115893</t>
+          <t>123839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147725</t>
+          <t>148917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131894</t>
+          <t>126312</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131894</t>
+          <t>126312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131894</t>
+          <t>126312</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77118</t>
+          <t>78769</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77118</t>
+          <t>78769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77118</t>
+          <t>78769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>209012</t>
+          <t>205081</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>209012</t>
+          <t>205081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>209012</t>
+          <t>205081</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81638</t>
+          <t>87977</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62499</t>
+          <t>70892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99601</t>
+          <t>107239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43710</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>35332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54296</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>125348</t>
+          <t>132898</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104635</t>
+          <t>112457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146072</t>
+          <t>152996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>163363</t>
+          <t>168268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145400</t>
+          <t>149006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182502</t>
+          <t>185353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>120486</t>
+          <t>123990</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109900</t>
+          <t>113078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>133579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>283849</t>
+          <t>292258</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263125</t>
+          <t>272160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>304562</t>
+          <t>312699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>245001</t>
+          <t>256245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245001</t>
+          <t>256245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245001</t>
+          <t>256245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>164196</t>
+          <t>168911</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164196</t>
+          <t>168911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>164196</t>
+          <t>168911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>425156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>425156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>425156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69658</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58454</t>
+          <t>60537</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79500</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>98330</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82320</t>
+          <t>83914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108846</t>
+          <t>113098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69556</t>
+          <t>71626</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59714</t>
+          <t>61572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80760</t>
+          <t>83106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83833</t>
+          <t>84537</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75399</t>
+          <t>76984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>91181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>153389</t>
+          <t>156163</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140459</t>
+          <t>141395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166985</t>
+          <t>170579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>139214</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139214</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>139214</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110091</t>
+          <t>110850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110091</t>
+          <t>110850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110091</t>
+          <t>110850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>249305</t>
+          <t>254493</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>249305</t>
+          <t>254493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>249305</t>
+          <t>254493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>46464</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51594</t>
+          <t>61030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>68016</t>
+          <t>77211</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>62696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>95888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>128826</t>
+          <t>149612</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116342</t>
+          <t>135046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138531</t>
+          <t>161598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>99477</t>
+          <t>110992</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107374</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>228302</t>
+          <t>260604</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212439</t>
+          <t>241927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242097</t>
+          <t>275119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>128383</t>
+          <t>141739</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128383</t>
+          <t>141739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>128383</t>
+          <t>141739</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>296318</t>
+          <t>337815</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>296318</t>
+          <t>337815</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>296318</t>
+          <t>337815</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31415</t>
+          <t>36534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>47099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28310</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>65092</t>
+          <t>72686</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>65915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70252</t>
+          <t>79156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>97822</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>97822</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>97822</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>50353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41443</t>
+          <t>40481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>68862</t>
+          <t>69044</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58483</t>
+          <t>58506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80155</t>
+          <t>80195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>69958</t>
+          <t>70158</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60787</t>
+          <t>60543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78995</t>
+          <t>80030</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>41696</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46325</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>110678</t>
+          <t>111853</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99385</t>
+          <t>100702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121057</t>
+          <t>122391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120438</t>
+          <t>120511</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120438</t>
+          <t>120511</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120438</t>
+          <t>120511</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>179540</t>
+          <t>180897</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>179540</t>
+          <t>180897</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>179540</t>
+          <t>180897</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>121095</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91288</t>
+          <t>101795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128999</t>
+          <t>139819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56839</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84453</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>177719</t>
+          <t>194821</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154638</t>
+          <t>170035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204642</t>
+          <t>217110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>208283</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162681</t>
+          <t>189559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200392</t>
+          <t>227583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>175868</t>
+          <t>207274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>160544</t>
+          <t>193174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188158</t>
+          <t>221514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>358958</t>
+          <t>415557</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>332035</t>
+          <t>393268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>382039</t>
+          <t>440343</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>291680</t>
+          <t>329378</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>291680</t>
+          <t>329378</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>291680</t>
+          <t>329378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>244997</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244997</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>244997</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>536677</t>
+          <t>610378</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>536677</t>
+          <t>610378</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>536677</t>
+          <t>610378</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>68164</t>
+          <t>75542</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19881</t>
+          <t>61887</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135273</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>35688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>90607</t>
+          <t>101304</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>85074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148285</t>
+          <t>119878</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>456715</t>
+          <t>241929</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>389606</t>
+          <t>225710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>504998</t>
+          <t>255584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>129200</t>
+          <t>147493</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120267</t>
+          <t>137567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136150</t>
+          <t>155357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>585915</t>
+          <t>389422</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>528237</t>
+          <t>370848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>643627</t>
+          <t>405652</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>524879</t>
+          <t>317471</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>524879</t>
+          <t>317471</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>524879</t>
+          <t>317471</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>151642</t>
+          <t>173255</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>151642</t>
+          <t>173255</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>151642</t>
+          <t>173255</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>676522</t>
+          <t>490726</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>676522</t>
+          <t>490726</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>676522</t>
+          <t>490726</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>296898</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>587979</t>
+          <t>557676</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210736</t>
+          <t>223224</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>259962</t>
+          <t>273858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>509845</t>
+          <t>720426</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>811062</t>
+          <t>809577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1181651</t>
+          <t>1027450</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1081641</t>
+          <t>988778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1372722</t>
+          <t>1066109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>738651</t>
+          <t>808051</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>713749</t>
+          <t>782056</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>762975</t>
+          <t>832690</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1920302</t>
+          <t>1835501</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1832269</t>
+          <t>1792791</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2133486</t>
+          <t>1881942</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
